--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±14分钟</t>
+          <t>07:20采样：该车到重点站沪南路御桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±10分钟</t>
+          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数168分钟估算，约±10分钟</t>
+          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>5/19</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1340,22 +1340,26 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,17 +1391,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1407,13 +1411,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>173.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>13/19</t>
         </is>
       </c>
     </row>
@@ -1421,24 +1429,24 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1451,34 +1459,34 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数156分钟估算，约±6分钟</t>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,32 +1515,1317 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>14/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>172分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>12/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>167分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>165分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>164分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数156分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>156.0</t>
         </is>
       </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>4/8</t>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>6/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,11 +449,11 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -642,26 +642,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 37分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +689,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -756,29 +752,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路御桥路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +808,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -837,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -880,26 +876,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 46分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -907,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -951,17 +943,13 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -999,26 +987,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 70分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1026,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1050,17 +1034,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1070,17 +1054,13 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1088,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1141,7 +1121,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,10 +1129,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq29映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1170,7 +1162,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1191,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1340,24 +1332,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±10分钟</t>
+          <t>08:10采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,12 +1408,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1459,24 +1451,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>177分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1486,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,7 +1502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
@@ -1535,12 +1527,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/19</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1570,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±9分钟</t>
+          <t>08:01采样：该车到重点站沪南路高科西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1605,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,7 +1621,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1654,12 +1646,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1689,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±11分钟</t>
+          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1748,7 +1740,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1773,12 +1765,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/19</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1808,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1867,7 +1859,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -1892,12 +1884,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -1935,24 +1927,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1962,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2003,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2058,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数153分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2081,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/19</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2177,12 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数156分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2200,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2229,7 +2221,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2254,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2357,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2373,24 +2365,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2403,24 +2395,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数161分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2430,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2454,12 +2446,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2479,12 +2471,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/19</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2484,7 @@
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2502,7 +2494,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2540,12 +2532,12 @@
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2559,7 +2551,7 @@
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2595,7 +2587,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2603,24 +2595,24 @@
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2633,22 +2625,26 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2656,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2680,17 +2676,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2700,13 +2696,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2744,34 +2744,34 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数149分钟估算，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2795,37 +2795,957 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>4/19</t>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>12/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>147分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -647,17 +647,21 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 37分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -714,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -757,12 +761,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -784,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -871,27 +875,31 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -899,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -923,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -943,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -987,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 70分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 58分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1010,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1109,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1121,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1244,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1332,19 +1348,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1359,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1408,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -1451,19 +1467,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>177分钟</t>
+          <t>180分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±11分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1478,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1527,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -1570,24 +1586,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站沪南路高科西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
+          <t>08:20采样：该车到重点站迎春路金松路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1597,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1621,7 +1637,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1646,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1689,19 +1705,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±8分钟</t>
+          <t>08:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1716,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1765,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1836,12 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±13分钟</t>
+          <t>08:20采样：该车到重点站迎春路金松路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1835,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1859,7 +1875,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -1889,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2062,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2058,12 +2074,12 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2073,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -2165,24 +2181,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
+          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2192,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2216,7 +2232,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2241,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,7 +2641,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2637,7 +2653,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2652,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2825,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -2863,24 +2879,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2939,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3227,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3338,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3507,7 +3523,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3626,7 +3642,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3740,12 +3756,250 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 58分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:01采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq35，推进7站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1237,19 +1237,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>177分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 17分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1284,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>20/26</t>
         </is>
       </c>
     </row>
@@ -1348,26 +1352,22 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:11采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -1467,26 +1467,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>180分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:50采样，终点ETA 52分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1518,37 +1514,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -1586,26 +1582,22 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站迎春路金松路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1613,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1642,7 +1634,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1652,22 +1644,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1700,29 +1692,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1756,12 +1748,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1771,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -1824,26 +1816,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>181分钟</t>
+          <t>179分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站迎春路金松路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1851,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1875,12 +1863,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1900,12 +1888,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>179.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>21/26</t>
         </is>
       </c>
     </row>
@@ -1943,24 +1931,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+          <t>09:21采样：该车到重点站金杨路金口路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1970,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2007,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -2062,24 +2050,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±8分钟</t>
+          <t>09:11采样：该车到重点站康沈路秀沿路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2126,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -2181,24 +2169,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±12分钟</t>
+          <t>09:21采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,7 +2220,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
@@ -2257,12 +2245,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -2300,22 +2288,26 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>09:11采样：该车到重点站锦绣路罗山路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2323,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2347,17 +2339,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2367,13 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -2411,19 +2407,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>183分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数161分钟，约±6分钟</t>
+          <t>09:21采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2438,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,7 +2483,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2553,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2641,19 +2637,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
+          <t>09:21采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2668,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2713,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2837,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -2879,24 +2875,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+          <t>09:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2906,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3132,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,22 +3216,26 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>08:33采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3287,13 +3287,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,24 +3446,24 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3469,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3498,7 +3502,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3518,12 +3522,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -3561,24 +3565,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±15分钟</t>
+          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3588,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3612,12 +3616,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3637,12 +3641,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3680,19 +3684,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数147分钟估算，约±5分钟</t>
+          <t>09:21采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3707,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3736,7 +3740,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3756,12 +3760,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -3799,24 +3803,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站康沈路秀康路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3826,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3855,7 +3859,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3875,12 +3879,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -3888,24 +3892,24 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3918,24 +3922,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±8分钟</t>
+          <t>09:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3945,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3959,47 +3963,864 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>09:21采样：该车到重点站博兴路兰城路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
-      <c r="W30" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>20/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X30" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>2/26</t>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>14/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1237,19 +1237,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>177分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 17分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:31采样，终点ETA 3分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>22/26</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1594,10 +1594,14 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,12 +1633,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1654,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1701,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -1816,19 +1820,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>179分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:21采样，终点ETA 44分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:50采样，终点ETA 10分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1863,7 +1867,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
@@ -1878,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>179.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/26</t>
+          <t>23/26</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1930,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1943,7 +1947,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站金杨路金口路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,12 +1986,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -2045,24 +2049,24 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>09:11采样：该车到重点站康沈路秀沿路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2101,12 +2105,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2116,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -2169,24 +2173,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±10分钟</t>
+          <t>同车下一次反向发车10:30，减去该车自身同类时段历史终点停站中位数18分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2220,12 +2224,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2235,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -2288,26 +2292,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>09:11采样：该车到重点站锦绣路罗山路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:01采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -2402,29 +2402,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>17/26</t>
         </is>
       </c>
     </row>
@@ -2521,27 +2521,31 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,17 +2577,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2593,13 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>21/26</t>
         </is>
       </c>
     </row>
@@ -2637,26 +2645,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:01采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2693,7 +2697,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2703,17 +2707,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2874,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2880,14 +2884,14 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2926,12 +2930,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2951,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3128,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3216,19 +3220,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>08:33采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+          <t>10:01采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3243,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3292,12 +3296,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>20/26</t>
         </is>
       </c>
     </row>
@@ -3335,22 +3339,26 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>10:01采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3358,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3382,17 +3390,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3402,13 +3410,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -3446,19 +3458,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3473,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3522,12 +3534,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>19/26</t>
         </is>
       </c>
     </row>
@@ -3565,24 +3577,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站沪南路华夏西路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±8分钟</t>
+          <t>10:11采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3592,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3641,12 +3653,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -3684,19 +3696,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3711,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3760,12 +3772,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -3803,24 +3815,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站康沈路秀康路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±10分钟</t>
+          <t>10:20采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3830,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3879,12 +3891,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3922,24 +3934,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±6分钟</t>
+          <t>10:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3949,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3998,12 +4010,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -4041,19 +4053,19 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>09:21采样：该车到重点站博兴路兰城路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站浦建路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4068,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4117,12 +4129,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,24 +4283,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±8分钟</t>
+          <t>10:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4298,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4327,7 +4339,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4347,12 +4359,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4382,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4413,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4432,7 +4444,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4462,12 +4474,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>22/26</t>
         </is>
       </c>
     </row>
@@ -4475,24 +4487,24 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4505,19 +4517,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4527,12 +4539,12 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4561,7 +4573,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4576,17 +4588,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>13/26</t>
         </is>
       </c>
     </row>
@@ -4594,24 +4606,24 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4624,34 +4636,34 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>10:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4665,7 +4677,7 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4680,7 +4692,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4695,17 +4707,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -4743,22 +4755,26 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>10:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4766,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4790,37 +4806,985 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站莱阳路东陆路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>17/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>14/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>17/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/26</t>
+          <t>24/26</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/26</t>
+          <t>21/26</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>20/26</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/26</t>
+          <t>23/26</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3104,27 +3104,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3132,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3156,17 +3160,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3176,13 +3180,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>14/26</t>
         </is>
       </c>
     </row>
@@ -3215,29 +3223,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:01采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3247,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3271,12 +3279,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3286,22 +3294,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>156.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>22/26</t>
         </is>
       </c>
     </row>
@@ -3334,24 +3342,24 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10:01采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3366,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3390,12 +3398,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3405,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3461,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3470,12 +3478,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3485,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3509,12 +3517,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3604,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>7/26</t>
         </is>
       </c>
     </row>
@@ -3691,24 +3699,24 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3723,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3747,12 +3755,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3772,12 +3780,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3818,24 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3842,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3866,12 +3874,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3891,12 +3899,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>4/26</t>
         </is>
       </c>
     </row>
@@ -3929,24 +3937,24 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3961,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,12 +3993,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4000,22 +4008,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -4048,24 +4056,24 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站浦建路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4080,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,12 +4112,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4119,22 +4127,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>9/26</t>
         </is>
       </c>
     </row>
@@ -4162,12 +4170,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4195,18 +4203,34 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4224,7 +4248,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4278,29 +4302,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4310,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4334,12 +4358,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4359,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>18/26</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/26</t>
+          <t>24/26</t>
         </is>
       </c>
     </row>
@@ -4517,24 +4541,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
+          <t>11:21采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4544,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/26</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -4636,24 +4660,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
+          <t>11:21采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4663,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4712,7 +4736,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4755,19 +4779,19 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>11:21采样：该车到重点站金杨路金口路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -4782,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4831,12 +4855,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -4874,22 +4898,26 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>11:21采样：该车到重点站沪南路北中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4897,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4921,17 +4949,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4941,17 +4969,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/26</t>
+          <t>21/26</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5029,7 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>11:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -5016,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,24 +5136,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站莱阳路东陆路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±6分钟</t>
+          <t>11:21采样：该车到重点站浦建路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5135,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5184,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -5232,19 +5260,19 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5254,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5283,7 +5311,7 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5303,12 +5331,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/26</t>
         </is>
       </c>
     </row>
@@ -5351,14 +5379,14 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±5分钟</t>
+          <t>11:21采样：该车到重点站迎春路长柳路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -5373,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5402,7 +5430,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5422,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>15/26</t>
         </is>
       </c>
     </row>
@@ -5465,24 +5493,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±10分钟</t>
+          <t>11:21采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5492,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5521,7 +5549,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5541,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>17/26</t>
+          <t>20/26</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5673,24 +5701,24 @@
       <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5703,26 +5731,22 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5730,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5754,37 +5778,989 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>23/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>11:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>11:21采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X45" s="2" t="inlineStr">
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>153分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>11:21采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>156.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>2/26</t>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>12/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>7/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>9/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/26</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/26</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/26</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/26</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/26</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/26</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/26</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4307,24 +4307,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/26</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4421,27 +4421,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4449,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,17 +4477,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4493,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/26</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4536,29 +4540,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4568,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,12 +4596,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4617,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4655,24 +4659,24 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站长岛路张杨北路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4711,12 +4715,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4726,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4736,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4779,26 +4783,22 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站金杨路金口路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:01采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4893,29 +4893,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站沪南路北中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/26</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5012,29 +5012,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5083,22 +5083,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5131,24 +5131,24 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站浦建路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5250,29 +5250,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/26</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5374,26 +5374,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站迎春路长柳路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 12分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5401,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5430,7 +5426,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5450,12 +5446,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/26</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5493,24 +5489,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±8分钟</t>
+          <t>12:21采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5520,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5565,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/26</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5612,24 +5608,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±8分钟</t>
+          <t>同车下一次反向发车13:20，减去该车自身同类时段历史终点停站中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5639,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5668,7 +5664,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5678,22 +5674,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/26</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5846,24 +5842,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±11分钟</t>
+          <t>12:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5873,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,7 +5893,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
@@ -5922,12 +5918,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5965,19 +5961,19 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站关岳路康达路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数115分钟，约±6分钟</t>
+          <t>12:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -5992,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6041,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6084,24 +6080,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站莱阳路东陆路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±9分钟</t>
+          <t>12:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6111,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6160,12 +6156,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>156.5</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/26</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6203,24 +6199,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
+          <t>12:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6230,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6259,7 +6255,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6279,12 +6275,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6318,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -6334,12 +6330,12 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±10分钟</t>
+          <t>12:21采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6349,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,12 +6369,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6403,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/26</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6441,24 +6437,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
+          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6468,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,12 +6488,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6517,12 +6513,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6560,19 +6556,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±15分钟</t>
+          <t>12:21采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数122分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6587,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6616,7 +6612,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6636,12 +6632,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/26</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6687,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±12分钟</t>
+          <t>12:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6706,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6735,32 +6731,734 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>139.7</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>8/26</t>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3175,14 +3175,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>143.0</t>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,17 +3299,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5255,24 +5255,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5369,27 +5369,31 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5421,12 +5425,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5436,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5484,29 +5488,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,12 +5544,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5565,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5722,27 +5726,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5750,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5782,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5794,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5837,29 +5845,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5869,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,12 +5901,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5918,12 +5926,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5956,29 +5964,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路罗山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5988,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,12 +6020,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6027,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6080,26 +6088,22 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:50采样，终点ETA 46分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,17 +6135,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6151,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6199,24 +6203,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±7分钟</t>
+          <t>12:50采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6275,7 +6279,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6318,24 +6322,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±13分钟</t>
+          <t>12:50采样：该车到重点站沪南路御桥路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6345,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6394,12 +6398,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6437,19 +6441,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±12分钟</t>
+          <t>12:50采样：该车到重点站迎春路金松路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6464,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6513,12 +6517,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6572,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数122分钟，约±15分钟</t>
+          <t>12:50采样：该车到重点站丁香路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6583,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6637,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6691,12 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±12分钟</t>
+          <t>12:50采样：该车到重点站沪南路高科西路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6794,22 +6798,26 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>12:50采样：该车到重点站浦建路锦绣路 ETA 50分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,17 +6849,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6861,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7020,24 +7028,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±7分钟</t>
+          <t>12:50采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7047,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7076,7 +7084,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7096,7 +7104,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7166,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7285,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7404,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7458,7 +7466,360 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>122分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数122分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,17 +3299,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5731,24 +5731,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5797,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6083,27 +6083,31 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:50采样，终点ETA 46分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6139,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6155,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6203,26 +6207,22 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6322,26 +6322,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站沪南路御桥路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:18采样，终点ETA 29分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6349,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6378,7 +6374,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6398,7 +6394,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6441,24 +6437,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站迎春路金松路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±12分钟</t>
+          <t>13:18采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6468,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,7 +6488,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
@@ -6517,12 +6513,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6556,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6572,12 +6568,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站丁香路锦绣路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±14分钟</t>
+          <t>13:18采样：该车到重点站沪南路北中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6679,24 +6675,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站沪南路高科西路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±15分钟</t>
+          <t>13:18采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6706,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6755,12 +6751,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6798,19 +6794,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站浦建路锦绣路 ETA 50分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±14分钟</t>
+          <t>13:18采样：该车到重点站浦建路锦绣路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6825,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6874,12 +6870,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7028,7 +7024,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -7040,12 +7036,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12:50采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±9分钟</t>
+          <t>13:18采样：该车到重点站沪南路高科西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7055,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7147,19 +7143,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>13:18采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7174,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7203,7 +7199,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7223,12 +7219,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7274,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>13:18采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7293,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7322,7 +7318,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7412,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7462,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7650,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7699,7 +7695,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7765,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7819,7 +7815,241 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>152.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,17 +3770,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4127,22 +4127,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,22 +4611,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6088,24 +6088,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6202,27 +6202,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,12 +6258,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6279,12 +6283,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6317,27 +6321,31 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:18采样，终点ETA 29分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -6345,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,12 +6377,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6394,7 +6402,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6432,29 +6440,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,12 +6496,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6503,22 +6511,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6551,29 +6559,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站沪南路北中路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±11分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6583,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,12 +6615,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6632,7 +6640,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6670,29 +6678,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±11分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6702,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,12 +6734,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6741,22 +6749,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6789,29 +6797,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站浦建路锦绣路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6821,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,12 +6853,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6870,12 +6878,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6911,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq48，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6936,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6944,10 +6952,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6965,7 +6989,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7019,29 +7043,29 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站沪南路高科西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7051,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,12 +7099,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7090,17 +7114,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7143,24 +7167,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7170,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7219,12 +7243,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7262,24 +7286,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:18采样：该车到重点站川周公路康沈路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±6分钟</t>
+          <t>14:20采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7289,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7338,12 +7362,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7500,24 +7524,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>14:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7527,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7551,12 +7575,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7576,12 +7600,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7619,19 +7643,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数122分钟估算，约±5分钟</t>
+          <t>14:20采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7646,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7675,7 +7699,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7695,12 +7719,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7738,22 +7762,26 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>14:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7761,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7785,17 +7813,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7805,12 +7833,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7853,19 +7881,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>14:20采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7880,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7909,7 +7937,7 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7929,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7995,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,6 +8081,597 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>136.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,18 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3185,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,12 +3427,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3780,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4137,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4269,7 +4273,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4378,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5812,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,12 +6763,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6806,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6829,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6878,12 +6882,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6920,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq48，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6944,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7010,7 +7014,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7048,12 +7052,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -7075,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7162,29 +7166,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站沪南路御桥路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7194,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,12 +7222,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7243,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7281,24 +7285,24 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,12 +7341,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7362,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7519,29 +7523,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站锦绣路花木路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7551,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,12 +7579,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7600,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7643,26 +7647,22 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7762,26 +7762,22 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7789,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,12 +7809,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7838,12 +7834,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7876,24 +7872,24 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站莱阳路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7908,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,12 +7928,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7957,12 +7953,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8077,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8115,19 +8111,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8142,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8171,7 +8167,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8191,12 +8187,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8234,24 +8230,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±8分钟</t>
+          <t>15:21采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8261,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8290,7 +8286,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8310,12 +8306,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8353,19 +8349,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8380,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8409,7 +8405,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8429,12 +8425,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8472,22 +8468,26 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>15:11采样：该车到重点站康丽路康恩路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数154分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,17 +8519,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8539,17 +8539,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,12 +8663,591 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>146.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>135.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>150.5</t>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,14 +3536,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>148.0</t>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,14 +3655,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,14 +3893,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>135.5</t>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,14 +4849,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>150.5</t>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,22 +5563,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,22 +6634,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,17 +7356,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7528,24 +7528,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7659,7 +7659,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 27分钟</t>
+          <t>SHMAAS末次终点ETA推算：15:41采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
@@ -7757,27 +7757,31 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 44分钟</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7785,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,12 +7813,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7834,12 +7838,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7877,19 +7881,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7904,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7953,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7991,27 +7995,31 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -8019,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,17 +8051,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8063,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8106,29 +8114,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站白桦路明月路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8138,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,12 +8170,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8187,12 +8195,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8230,26 +8238,22 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 33分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8257,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,12 +8285,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8306,12 +8310,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8349,26 +8353,22 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 67分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,17 +8400,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8420,17 +8420,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8468,24 +8468,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>15:11采样：该车到重点站康丽路康恩路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数154分钟，约±5分钟</t>
+          <t>16:21采样：该车到重点站云山路碧云路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8587,19 +8587,19 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8817,24 +8817,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8936,24 +8936,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9012,12 +9012,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9055,24 +9055,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±13分钟</t>
+          <t>16:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9144,22 +9144,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9192,12 +9192,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9211,43 +9211,1098 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr"/>
-      <c r="AC74" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站莱阳路东陆路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>152分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数152分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>153.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:29</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>140.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,12 +2239,12 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,14 +2592,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,17 +4854,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,22 +5682,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,14 +5801,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,22 +6872,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,22 +7709,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8066,14 +8066,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8119,24 +8119,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8233,27 +8233,31 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 33分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8261,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8285,12 +8289,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8300,22 +8304,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8353,19 +8357,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 67分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:01采样，终点ETA 14分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr"/>
@@ -8376,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,17 +8404,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8420,17 +8424,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8473,21 +8477,17 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站云山路碧云路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:10采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8534,22 +8534,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8582,29 +8582,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8737,10 +8737,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8758,7 +8774,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8817,26 +8833,22 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:10采样，终点ETA 55分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8844,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,17 +8880,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8888,17 +8900,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8936,24 +8948,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站金杨路云山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±6分钟</t>
+          <t>17:20采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8963,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9055,24 +9067,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±7分钟</t>
+          <t>17:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9082,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,7 +9118,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
@@ -9131,12 +9143,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9174,22 +9186,26 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9197,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,17 +9237,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9241,17 +9257,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9400,19 +9416,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±11分钟</t>
+          <t>17:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9427,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9476,7 +9492,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9519,24 +9535,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站莱阳路东陆路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+          <t>17:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9546,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9595,7 +9611,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9638,24 +9654,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±12分钟</t>
+          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9665,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9689,12 +9705,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9714,12 +9730,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9834,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9872,24 +9888,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数152分钟估算，约±9分钟</t>
+          <t>17:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9899,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9928,7 +9944,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9948,7 +9964,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>155.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9991,22 +10007,26 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10014,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10038,17 +10058,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10058,17 +10078,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -10106,22 +10126,26 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10129,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10153,17 +10177,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10173,17 +10197,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10221,24 +10245,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±7分钟</t>
+          <t>17:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10248,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10277,32 +10301,980 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:43</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y83" s="2" t="inlineStr">
+      <c r="Y86" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB83" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>140.8</t>
         </is>
       </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>17/30</t>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>144.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>155.7</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,12 +2478,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,22 +3298,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>155.7</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,22 +7594,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>145.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8653,22 +8653,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8833,19 +8833,19 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:10采样，终点ETA 55分钟</t>
+          <t>SHMAAS末次终点ETA推算：17:51采样，终点ETA 9分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,37 +8880,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8943,24 +8943,24 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -9062,29 +9062,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,12 +9118,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9181,29 +9181,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9252,22 +9252,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9416,26 +9416,22 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:11采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9443,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9467,17 +9463,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9487,12 +9483,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9535,26 +9531,22 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9562,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9586,12 +9578,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9611,12 +9603,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9654,19 +9646,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9681,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9720,22 +9712,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9850,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9888,19 +9880,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:23</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9915,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9964,7 +9956,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>155.7</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10007,24 +9999,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
+          <t>18:21采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10034,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,7 +10050,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
@@ -10083,12 +10075,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10126,19 +10118,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站浦建路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10153,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10202,12 +10194,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -10245,24 +10237,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±6分钟</t>
+          <t>18:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10272,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10321,12 +10313,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10379,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10441,7 +10433,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10471,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -10491,7 +10483,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站锦绣路花木路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10506,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10560,7 +10552,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10598,19 +10590,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10625,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10654,7 +10646,7 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10674,12 +10666,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10717,19 +10709,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10744,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10773,7 +10765,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10793,12 +10785,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10917,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10955,24 +10947,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±15分钟</t>
+          <t>18:21采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10982,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11011,7 +11003,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11031,12 +11023,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11074,19 +11066,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11101,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11130,7 +11122,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11150,12 +11142,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11193,19 +11185,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11220,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11249,32 +11241,853 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>145.2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数122分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数142分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y91" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z91" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>144.8</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>20/30</t>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,22 +7356,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9411,27 +9411,31 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:11采样，终点ETA 50分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9439,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9463,17 +9467,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9483,17 +9487,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9526,27 +9530,31 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9554,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9578,12 +9586,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9593,22 +9601,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9646,26 +9654,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:31采样，终点ETA 48分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9673,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9697,17 +9701,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9717,12 +9721,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9765,19 +9769,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：18:31采样，终点ETA 32分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
@@ -9788,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,37 +9816,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9880,19 +9884,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:12</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站康沈路秀沿路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9907,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9956,12 +9960,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9999,24 +10003,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±6分钟</t>
+          <t>18:31采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10026,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10075,12 +10079,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10118,19 +10122,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站浦建路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10145,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10194,12 +10198,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10242,14 +10246,14 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10264,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10313,12 +10317,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10471,7 +10475,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -10483,7 +10487,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站锦绣路花木路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10498,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10595,14 +10599,14 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站迎春路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10617,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10666,7 +10670,7 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10714,14 +10718,14 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10736,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10785,12 +10789,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10947,19 +10951,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±11分钟</t>
+          <t>18:31采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -10974,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11023,12 +11027,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11066,19 +11070,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11093,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11142,7 +11146,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11197,7 +11201,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11212,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11304,19 +11308,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数122分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11331,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11380,7 +11384,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11423,19 +11427,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数142分钟，约±5分钟</t>
+          <t>18:31采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数134分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11450,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11499,7 +11503,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11565,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11619,7 +11623,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11688,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11803,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11918,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11972,7 +11976,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11980,24 +11984,24 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12010,30 +12014,34 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12047,47 +12055,281 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>142.2</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
           <t>19:10</t>
         </is>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="X98" s="2" t="inlineStr">
-        <is>
-          <t>证据不足</t>
-        </is>
-      </c>
-      <c r="Y98" s="2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z98" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA98" s="2" t="inlineStr">
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>149.3</t>
-        </is>
-      </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>23/30</t>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>145.7</t>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>145.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2597,17 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,14 +3655,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,22 +4849,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>145.7</t>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,22 +5563,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>145.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,14 +6396,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9133,14 +9133,14 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>145.7</t>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9416,24 +9416,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9482,22 +9482,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>145.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9535,24 +9535,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -9649,27 +9649,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:31采样，终点ETA 48分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9677,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9701,17 +9705,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9721,17 +9725,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9768,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9774,17 +9778,21 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:31采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9792,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9816,12 +9824,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9841,12 +9849,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9884,26 +9892,22 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站康沈路秀沿路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:02采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9911,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9940,7 +9944,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9950,22 +9954,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -10015,14 +10019,10 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站长岛路张杨北路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:02采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10069,14 +10069,14 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10117,29 +10117,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10188,22 +10188,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>150.3</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -10236,29 +10236,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10355,27 +10355,31 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -10383,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,17 +10411,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10427,17 +10431,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10470,29 +10474,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:43</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10502,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10526,12 +10530,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10551,12 +10555,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10594,19 +10598,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站迎春路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站康沈路秀沿路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10621,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10670,12 +10674,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10713,19 +10717,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数92分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10740,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10789,12 +10793,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10956,19 +10960,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站白桦路明月路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
+          <t>19:21采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10978,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11002,7 +11006,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
@@ -11027,12 +11031,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11070,19 +11074,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11097,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11146,12 +11150,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11189,19 +11193,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站金杨路金业路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11216,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11265,12 +11269,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>145.2</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -11308,19 +11312,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站云山路碧云路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11335,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11384,12 +11388,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11427,19 +11431,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:52</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>18:31采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数134分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -11454,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11503,12 +11507,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11623,7 +11627,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11661,19 +11665,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11688,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11717,7 +11721,7 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11737,12 +11741,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11780,24 +11784,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±10分钟</t>
+          <t>19:21采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11807,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11831,12 +11835,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11856,12 +11860,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -11899,22 +11903,26 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11922,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,17 +11954,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11966,17 +11974,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -11984,24 +11992,24 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12014,34 +12022,30 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12055,7 +12059,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12065,17 +12069,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12085,17 +12089,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -12103,24 +12107,24 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12133,30 +12137,34 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12170,27 +12178,27 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12200,17 +12208,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -12218,24 +12226,24 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12248,26 +12256,22 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12275,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12289,47 +12293,749 @@
       <c r="T100" s="2" t="inlineStr"/>
       <c r="U100" s="2" t="inlineStr">
         <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>145.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W100" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>6/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>16/30</t>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>151.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>27/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>21:44</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>145.8</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>1/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>26/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,17 +2239,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,17 +3065,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,22 +5920,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,17 +9019,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,17 +9138,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,17 +10074,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10322,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10360,24 +10360,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10593,29 +10593,29 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站康沈路秀沿路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,12 +10649,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10664,17 +10664,17 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10712,29 +10712,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10950,29 +10950,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -11069,24 +11069,24 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11188,24 +11188,24 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11244,12 +11244,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11431,26 +11431,22 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11458,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11487,7 +11483,7 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11497,22 +11493,22 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11545,27 +11541,31 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11597,17 +11597,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11617,17 +11617,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -11665,19 +11665,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站白桦路明月路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11784,24 +11784,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±13分钟</t>
+          <t>20:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
@@ -11860,12 +11860,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11903,19 +11903,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:24</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站沪南路御桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11979,7 +11979,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>148.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -12137,24 +12137,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+          <t>20:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12256,22 +12256,26 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12279,7 +12283,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12303,17 +12307,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12323,17 +12327,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12371,22 +12375,26 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>20:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12394,7 +12402,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12418,17 +12426,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12438,17 +12446,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -12486,24 +12494,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±8分钟</t>
+          <t>20:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12513,7 +12521,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12542,7 +12550,7 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12562,12 +12570,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -12605,22 +12613,26 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>20:21采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12628,7 +12640,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12652,17 +12664,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12672,17 +12684,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>146.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12732,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:44</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -12732,12 +12744,12 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±10分钟</t>
+          <t>20:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12747,7 +12759,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12776,7 +12788,7 @@
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12851,7 +12863,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+          <t>20:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -12866,7 +12878,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12895,7 +12907,7 @@
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12981,7 +12993,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13035,7 +13047,245 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>140.8</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>130.8</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-21-浦东35路.xlsx
+++ b/data/export/2026-09-21-浦东35路.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3903,12 +3903,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,17 +4854,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10193,17 +10193,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11274,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11426,27 +11426,31 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11454,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11478,12 +11482,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11503,12 +11507,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11546,24 +11550,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11573,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11622,12 +11626,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11660,24 +11664,24 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数19分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -11692,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,12 +11720,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11741,7 +11745,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11779,29 +11783,29 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11811,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11835,12 +11839,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11860,7 +11864,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11898,24 +11902,24 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路御桥路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11930,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11954,12 +11958,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11979,7 +11983,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>148.2</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12012,12 +12016,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12045,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12053,10 +12057,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12074,7 +12094,7 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12132,29 +12152,29 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12164,7 +12184,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12188,12 +12208,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12213,12 +12233,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -12251,29 +12271,29 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12283,7 +12303,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12307,12 +12327,12 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12332,7 +12352,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12365,36 +12385,32 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12402,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12410,10 +12426,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr"/>
-      <c r="R101" s="2" t="inlineStr"/>
-      <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12426,17 +12458,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12446,12 +12478,12 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12494,7 +12526,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -12506,12 +12538,12 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±6分钟</t>
+          <t>20:41采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12521,7 +12553,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12613,19 +12645,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>21:21采样：该车到重点站五莲路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12640,7 +12672,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12689,12 +12721,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -12732,26 +12764,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12759,7 +12787,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12783,12 +12811,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12808,12 +12836,12 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12851,24 +12879,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:07</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
+          <t>21:21采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12878,7 +12906,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12927,12 +12955,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -12970,22 +12998,26 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>20:51采样：该车到重点站锦绣路罗山路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12993,7 +13025,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13017,17 +13049,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13037,17 +13069,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -13097,12 +13129,12 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+          <t>21:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -13112,7 +13144,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13141,7 +13173,7 @@
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
@@ -13209,19 +13241,19 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+          <t>21:11采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -13231,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13260,7 +13292,7 @@
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
@@ -13280,12 +13312,12 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>130.8</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
